--- a/output/pdf_financials_xlsx/LEEF.xlsx
+++ b/output/pdf_financials_xlsx/LEEF.xlsx
@@ -431,6 +431,11 @@
   </sheetPr>
   <dimension ref="A1:C135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/LEEF.xlsx
+++ b/output/pdf_financials_xlsx/LEEF.xlsx
@@ -540,10 +540,10 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>0.440866</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>0.272957</v>
       </c>
     </row>
     <row r="10">
@@ -592,10 +592,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -644,10 +644,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>3.307243</v>
+        <v>-3.307243</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>2.518615</v>
+        <v>-2.518615</v>
       </c>
     </row>
     <row r="18">
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.507186</v>
+        <v>8.083608999999999</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.508987</v>
+        <v>6.556036</v>
       </c>
     </row>
     <row r="49">
@@ -2203,7 +2203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F150"/>
+  <dimension ref="A1:F151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E7" s="5" t="n">
@@ -4742,7 +4742,11 @@
           <t>Advertising and promotion</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E97" s="5" t="n">
         <v>0.440866</v>
       </c>
@@ -5508,17 +5512,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Additional Other shareholders Non- Total</t>
+          <t>Additional                            Other          shareholders        Non-             Total</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Net loss - - (17,629,675) - (17,629,675)</t>
+          <t>Balance, December 31, 2024 172,984,299 $ - $ 109,650,027 $ (121,747,435) $ (336,536) $ (12,433,944) $</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" s="5" t="n">
-        <v>-17.629675</v>
+        <v>-12.433944</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -5534,17 +5538,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Additional Other shareholders Non- Total</t>
+          <t>Additional                            Other          shareholders        Non-             Total</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Common shares issued for cash 8,363,560 - 241,889 - - 241,889</t>
+          <t>Net loss - - (17,629,675) - (17,629,675)</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" s="5" t="n">
-        <v>0.241889</v>
+        <v>-17.629675</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -5560,17 +5564,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Common shares issued for</t>
+          <t>Additional                            Other          shareholders        Non-             Total</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Common shares issued for services 1,465,219 - 248,365 - - 248,365</t>
+          <t>Common shares issued for cash 8,363,560 - 241,889 - - 241,889</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" s="5" t="n">
-        <v>0.248365</v>
+        <v>0.241889</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -5586,17 +5590,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Common shares issued for trade</t>
+          <t>Common shares issued for</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Common shares issued for trade payables 2,024,241 - 368,142 - - 368,142</t>
+          <t>Common shares issued for services 1,465,219 - 248,365 - - 248,365</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" s="5" t="n">
-        <v>0.368142</v>
+        <v>0.248365</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -5612,17 +5616,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Common shares issued for</t>
+          <t>Common shares issued for trade</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Common shares issued for earnout consideration 1,858,032 - 935,618 - - 935,618</t>
+          <t>Common shares issued for trade payables 2,024,241 - 368,142 - - 368,142</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
       <c r="E131" s="5" t="n">
-        <v>0.9356179999999999</v>
+        <v>0.368142</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -5643,12 +5647,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Foreign currency translation - - - - (343) (343)</t>
+          <t>Common shares issued for earnout consideration 1,858,032 - 935,618 - - 935,618</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" s="5" t="n">
-        <v>-0.000343</v>
+        <v>0.9356179999999999</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -5664,17 +5668,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>conversion of debentures and</t>
+          <t>Common shares issued for</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>conversion of debentures and related party notes payable 63,764,773 - 17,564,048 - - 17,564,048</t>
+          <t>Foreign currency translation - - - - (343) (343)</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" s="5" t="n">
-        <v>17.564048</v>
+        <v>-0.000343</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -5695,14 +5699,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Exercise of stock options 302,666 - - - - -</t>
+          <t>conversion of debentures and related party notes payable 63,764,773 - 17,564,048 - - 17,564,048</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E134" s="5" t="n">
+        <v>17.564048</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -5723,7 +5725,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Exercise of restricted stock units 7,185,206 - - - - -</t>
+          <t>Exercise of stock options 302,666 - - - - -</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
@@ -5751,12 +5753,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Stock compensation expense - - 967,579 - - 967,579</t>
+          <t>Exercise of restricted stock units 7,185,206 - - - - -</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
-      <c r="E136" s="5" t="n">
-        <v>0.967579</v>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -5772,17 +5776,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Equity based compensation for</t>
+          <t>conversion of debentures and</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Equity based compensation for restricted stock unit grants - - 1,470,020 - - 1,470,020</t>
+          <t>Stock compensation expense - - 967,579 - - 967,579</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" s="5" t="n">
-        <v>1.47002</v>
+        <v>0.967579</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -5803,12 +5807,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2025 257,947,996 $ - $131,445,688 $(139,377,110) $ (336,879) $ (8,268,301) $</t>
+          <t>Equity based compensation for restricted stock unit grants - - 1,470,020 - - 1,470,020</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" s="5" t="n">
-        <v>-8.268300999999999</v>
+        <v>1.47002</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -5829,15 +5833,17 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Activity for the Year Ended December</t>
+          <t>Balance, December 31, 2025 257,947,996 $ - $ 131,445,688 $ (139,377,110) $ (336,879) $ (8,268,301) $</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="F139" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>-8.268300999999999</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="140">
@@ -5848,20 +5854,20 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Additional Other shareholders Non- Total</t>
+          <t>Equity based compensation for</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2023 118,380,930 $ - $ 94,667,939 $ (97,125,921) $ (343,850) $ (2,801,832) $</t>
+          <t>Activity for the Year Ended December</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" s="5" t="n">
-        <v>0.847657</v>
+        <v>0.002024</v>
       </c>
       <c r="F140" s="5" t="n">
-        <v>3.649489</v>
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="141">
@@ -5872,22 +5878,20 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Additional Other shareholders Non- Total</t>
+          <t>Additional                            Other          shareholders       Non-             Total</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Net loss - - (24,621,514) - (24,621,514)</t>
+          <t>Balance, December 31, 2023 118,380,930 $ - $ 94,667,939 $ (97,125,921) $ (343,850) $ (2,801,832) $</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
       <c r="E141" s="5" t="n">
-        <v>-24.621514</v>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.847657</v>
+      </c>
+      <c r="F141" s="5" t="n">
+        <v>3.649489</v>
       </c>
     </row>
     <row r="142">
@@ -5898,17 +5902,17 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Additional Other shareholders Non- Total</t>
+          <t>Additional                            Other          shareholders       Non-             Total</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Common shares issued for cash 12,635,059 - 1,047,533 - - 1,047,533</t>
+          <t>Net loss - - (24,621,514) - (24,621,514)</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" s="5" t="n">
-        <v>1.047533</v>
+        <v>-24.621514</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -5924,17 +5928,17 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Common shares issued for</t>
+          <t>Additional                            Other          shareholders       Non-             Total</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Common shares issued for services 1,500,000 - 333,333 - 333,333</t>
+          <t>Common shares issued for cash 12,635,059 - 1,047,533 - - 1,047,533</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" s="5" t="n">
-        <v>0.333333</v>
+        <v>1.047533</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -5955,12 +5959,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Common shares issued for earnout consideration 17,491,400 - 1,900,000 - - 1,900,000</t>
+          <t>Common shares issued for services 1,500,000 - 333,333 - 333,333</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" s="5" t="n">
-        <v>1.9</v>
+        <v>0.333333</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -5981,12 +5985,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Foreign currency translation - - - 7,314 7,314</t>
+          <t>Common shares issued for earnout consideration 17,491,400 - 1,900,000 - - 1,900,000</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" s="5" t="n">
-        <v>0.007314</v>
+        <v>1.9</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -6002,17 +6006,17 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>conversion of notes payable and</t>
+          <t>Common shares issued for</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>conversion of notes payable and debentures 22,395,948 - 7,083,853 - - 7,083,853</t>
+          <t>Foreign currency translation - - - 7,314 7,314</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" s="5" t="n">
-        <v>7.083853</v>
+        <v>0.007314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -6028,22 +6032,22 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>controlling interest in Aya</t>
+          <t>conversion of notes payable and</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Biosciences 580,962 - 3,649,489 - - 3,649,489</t>
+          <t>conversion of notes payable and debentures 22,395,948 - 7,083,853 - - 7,083,853</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F147" s="5" t="n">
-        <v>-3.649489</v>
+      <c r="E147" s="5" t="n">
+        <v>7.083853</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="148">
@@ -6059,17 +6063,17 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Stock compensation expense - - 428,108 - - 428,108</t>
+          <t>Biosciences 580,962 - 3,649,489 - - 3,649,489</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
-      <c r="E148" s="5" t="n">
-        <v>0.428108</v>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F148" s="5" t="n">
+        <v>-3.649489</v>
       </c>
     </row>
     <row r="149">
@@ -6080,17 +6084,17 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Equity based compensation for</t>
+          <t>controlling interest in Aya</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Equity based compensation for restricted stock unit grants - - 539,772 - - 539,772</t>
+          <t>Stock compensation expense - - 428,108 - - 428,108</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" s="5" t="n">
-        <v>0.539772</v>
+        <v>0.428108</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -6111,14 +6115,40 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2024 172,984,299 $ - $109,650,027 $(121,747,435) $ (336,536) $(12,433,944) $</t>
+          <t>Equity based compensation for restricted stock unit grants - - 539,772 - - 539,772</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
       <c r="E150" s="5" t="n">
+        <v>0.539772</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Equity based compensation for</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2024 172,984,299 $ - $ 109,650,027 $ (121,747,435) $ (336,536) $ (12,433,944) $</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" s="5" t="n">
         <v>-12.433944</v>
       </c>
-      <c r="F150" t="inlineStr">
+      <c r="F151" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/output/pdf_financials_xlsx/LEEF.xlsx
+++ b/output/pdf_financials_xlsx/LEEF.xlsx
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>8.083608999999999</v>
+        <v>0.507186</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>6.556036</v>
+        <v>0.508987</v>
       </c>
     </row>
     <row r="49">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E7" s="5" t="n">

--- a/output/pdf_financials_xlsx/LEEF.xlsx
+++ b/output/pdf_financials_xlsx/LEEF.xlsx
@@ -867,10 +867,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.731979</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.190722</v>
       </c>
     </row>
     <row r="35">
@@ -893,10 +893,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.731979</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>2.190722</v>
       </c>
     </row>
     <row r="37">
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.507186</v>
+        <v>5.35163</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.508987</v>
+        <v>4.365314</v>
       </c>
     </row>
     <row r="49">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E7" s="5" t="n">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
